--- a/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_8.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1750162155_individual_h_8.xlsx
@@ -658,7 +658,7 @@
         <v>0.008471483344799909</v>
       </c>
       <c r="C2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>36040698</v>
+        <v>4103873</v>
       </c>
       <c r="L2" t="n">
-        <v>20034808</v>
+        <v>1963715</v>
       </c>
       <c r="M2" t="n">
-        <v>4861323</v>
+        <v>383012</v>
       </c>
       <c r="N2" t="n">
-        <v>256500</v>
+        <v>14811</v>
       </c>
       <c r="O2" t="n">
-        <v>2851100</v>
+        <v>219799</v>
       </c>
       <c r="P2" t="n">
-        <v>1143451</v>
+        <v>93223</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999901056289673</v>
+        <v>0.9999962449073792</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8726025223731995</v>
+        <v>0.7769218683242798</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7598530650138855</v>
+        <v>0.5956236124038696</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7059638500213623</v>
+        <v>0.5020797252655029</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3042423129081726</v>
+        <v>0.07789278030395508</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7538191080093384</v>
+        <v>0.5489910840988159</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8310737013816833</v>
+        <v>0.679948627948761</v>
       </c>
       <c r="X2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>50771040</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="AG2" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AH2" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AI2" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AK2" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9563227891921997</v>
+        <v>0.9555724859237671</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9114070534706116</v>
+        <v>0.9118132591247559</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580120801925659</v>
+        <v>0.8582125902175903</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6619145274162292</v>
+        <v>0.6612037420272827</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019697904586792</v>
+        <v>0.9019888043403625</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314440488815308</v>
+        <v>0.9314650297164917</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002029531499543211</v>
       </c>
       <c r="C3" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>36040698</v>
+        <v>4103873</v>
       </c>
       <c r="E3" t="n">
-        <v>4270959</v>
+        <v>888264</v>
       </c>
       <c r="F3" t="n">
-        <v>98106</v>
+        <v>29113</v>
       </c>
       <c r="G3" t="n">
-        <v>11777</v>
+        <v>3797</v>
       </c>
       <c r="H3" t="n">
-        <v>5698</v>
+        <v>1849</v>
       </c>
       <c r="I3" t="n">
-        <v>390</v>
+        <v>136</v>
       </c>
       <c r="J3" t="n">
-        <v>80556459</v>
+        <v>10069596</v>
       </c>
       <c r="K3" t="n">
-        <v>85638515</v>
+        <v>10210613</v>
       </c>
       <c r="L3" t="n">
-        <v>98689980</v>
+        <v>11773302</v>
       </c>
       <c r="M3" t="n">
-        <v>121820929</v>
+        <v>15097384</v>
       </c>
       <c r="N3" t="n">
-        <v>130025929</v>
+        <v>16150891</v>
       </c>
       <c r="O3" t="n">
-        <v>126318651</v>
+        <v>15724497</v>
       </c>
       <c r="P3" t="n">
-        <v>129548457</v>
+        <v>16178530</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8914864063262939</v>
+        <v>0.8163598775863647</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7616019248962402</v>
+        <v>0.5933557748794556</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6497083902359009</v>
+        <v>0.4079903960227966</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3584940731525421</v>
+        <v>0.164980947971344</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6991002559661865</v>
+        <v>0.4301914274692535</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7390826344490051</v>
+        <v>0.4815486371517181</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>38712019</v>
+        <v>4813274</v>
       </c>
       <c r="Z3" t="n">
-        <v>1591784</v>
+        <v>198388</v>
       </c>
       <c r="AA3" t="n">
-        <v>68580</v>
+        <v>8469</v>
       </c>
       <c r="AB3" t="n">
-        <v>54698</v>
+        <v>6867</v>
       </c>
       <c r="AC3" t="n">
-        <v>326</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>80556960</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>89132297</v>
+        <v>11165177</v>
       </c>
       <c r="AG3" t="n">
-        <v>102695121</v>
+        <v>12815311</v>
       </c>
       <c r="AH3" t="n">
-        <v>122784182</v>
+        <v>15344357</v>
       </c>
       <c r="AI3" t="n">
-        <v>130370832</v>
+        <v>16295858</v>
       </c>
       <c r="AJ3" t="n">
-        <v>126850187</v>
+        <v>15855036</v>
       </c>
       <c r="AK3" t="n">
-        <v>129674836</v>
+        <v>16209148</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575629830360413</v>
+        <v>0.9574769735336304</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099209904670715</v>
+        <v>0.9097115993499756</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8572890758514404</v>
+        <v>0.8566603064537048</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6613048911094666</v>
+        <v>0.6601800322532654</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9014734625816345</v>
+        <v>0.9011573195457458</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312471747398376</v>
+        <v>0.9310656785964966</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03203123381705863</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4936999</v>
+        <v>1090210</v>
       </c>
       <c r="E4" t="n">
-        <v>20034808</v>
+        <v>1963715</v>
       </c>
       <c r="F4" t="n">
-        <v>1149246</v>
+        <v>201603</v>
       </c>
       <c r="G4" t="n">
-        <v>74647</v>
+        <v>25825</v>
       </c>
       <c r="H4" t="n">
-        <v>100074</v>
+        <v>25030</v>
       </c>
       <c r="I4" t="n">
-        <v>10356</v>
+        <v>3123</v>
       </c>
       <c r="J4" t="n">
-        <v>501</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>5261838</v>
+        <v>1178348</v>
       </c>
       <c r="L4" t="n">
-        <v>6331879</v>
+        <v>1333191</v>
       </c>
       <c r="M4" t="n">
-        <v>2024756</v>
+        <v>379839</v>
       </c>
       <c r="N4" t="n">
-        <v>586578</v>
+        <v>175335</v>
       </c>
       <c r="O4" t="n">
-        <v>931107</v>
+        <v>180570</v>
       </c>
       <c r="P4" t="n">
-        <v>232421</v>
+        <v>43880</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999950528144836</v>
+        <v>0.999998152256012</v>
       </c>
       <c r="R4" t="n">
-        <v>0.88194340467453</v>
+        <v>0.7961527705192566</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7607264518737793</v>
+        <v>0.5944875478744507</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6766689419746399</v>
+        <v>0.4501712322235107</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3291476368904114</v>
+        <v>0.1058230921626091</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7254292964935303</v>
+        <v>0.4823845624923706</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7823833823204041</v>
+        <v>0.5638039112091064</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1650806</v>
+        <v>208961</v>
       </c>
       <c r="Z4" t="n">
-        <v>23936510</v>
+        <v>3010697</v>
       </c>
       <c r="AA4" t="n">
-        <v>664902</v>
+        <v>83070</v>
       </c>
       <c r="AB4" t="n">
-        <v>44224</v>
+        <v>5580</v>
       </c>
       <c r="AC4" t="n">
-        <v>9155</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>544</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1768056</v>
+        <v>223784</v>
       </c>
       <c r="AG4" t="n">
-        <v>2326738</v>
+        <v>291182</v>
       </c>
       <c r="AH4" t="n">
-        <v>1061503</v>
+        <v>132866</v>
       </c>
       <c r="AI4" t="n">
-        <v>241675</v>
+        <v>30368</v>
       </c>
       <c r="AJ4" t="n">
-        <v>399571</v>
+        <v>50031</v>
       </c>
       <c r="AK4" t="n">
-        <v>106042</v>
+        <v>13262</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9569424390792847</v>
+        <v>0.9565237760543823</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663366317749</v>
+        <v>0.9107611775398254</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576504588127136</v>
+        <v>0.8574357628822327</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6616095304489136</v>
+        <v>0.660691499710083</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9017215967178345</v>
+        <v>0.9015728235244751</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313456416130066</v>
+        <v>0.9312652945518494</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>222837</v>
+        <v>64758</v>
       </c>
       <c r="E5" t="n">
-        <v>1731615</v>
+        <v>356470</v>
       </c>
       <c r="F5" t="n">
-        <v>4861323</v>
+        <v>383012</v>
       </c>
       <c r="G5" t="n">
-        <v>194975</v>
+        <v>52761</v>
       </c>
       <c r="H5" t="n">
-        <v>428351</v>
+        <v>71064</v>
       </c>
       <c r="I5" t="n">
-        <v>43187</v>
+        <v>10711</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>4386949</v>
+        <v>923166</v>
       </c>
       <c r="L5" t="n">
-        <v>6271333</v>
+        <v>1345792</v>
       </c>
       <c r="M5" t="n">
-        <v>2620992</v>
+        <v>555765</v>
       </c>
       <c r="N5" t="n">
-        <v>458993</v>
+        <v>74963</v>
       </c>
       <c r="O5" t="n">
-        <v>1227142</v>
+        <v>291134</v>
       </c>
       <c r="P5" t="n">
-        <v>403671</v>
+        <v>100367</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999961853027344</v>
+        <v>0.9999985098838806</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9265291094779968</v>
+        <v>0.8719837665557861</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9040325880050659</v>
+        <v>0.83680659532547</v>
       </c>
       <c r="T5" t="n">
-        <v>0.96462482213974</v>
+        <v>0.9430065751075745</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9920384883880615</v>
+        <v>0.9847527742385864</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9835659861564636</v>
+        <v>0.9712656140327454</v>
       </c>
       <c r="W5" t="n">
-        <v>0.995156466960907</v>
+        <v>0.9912130236625671</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>64693</v>
+        <v>8176</v>
       </c>
       <c r="Z5" t="n">
-        <v>684803</v>
+        <v>86508</v>
       </c>
       <c r="AA5" t="n">
-        <v>6414507</v>
+        <v>804213</v>
       </c>
       <c r="AB5" t="n">
-        <v>79806</v>
+        <v>10008</v>
       </c>
       <c r="AC5" t="n">
-        <v>233442</v>
+        <v>29239</v>
       </c>
       <c r="AD5" t="n">
-        <v>5064</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1715628</v>
+        <v>213765</v>
       </c>
       <c r="AG5" t="n">
-        <v>2369631</v>
+        <v>298810</v>
       </c>
       <c r="AH5" t="n">
-        <v>1067808</v>
+        <v>134564</v>
       </c>
       <c r="AI5" t="n">
-        <v>242334</v>
+        <v>30507</v>
       </c>
       <c r="AJ5" t="n">
-        <v>401815</v>
+        <v>50502</v>
       </c>
       <c r="AK5" t="n">
-        <v>106369</v>
+        <v>13345</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734734296798706</v>
+        <v>0.9733461737632751</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642394185066223</v>
+        <v>0.9640599489212036</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837862849235535</v>
+        <v>0.9837091565132141</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.996314525604248</v>
+        <v>0.9962917566299438</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938978552818298</v>
+        <v>0.9938759207725525</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998382568359375</v>
+        <v>0.9983792304992676</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>91446</v>
+        <v>17730</v>
       </c>
       <c r="E6" t="n">
-        <v>135201</v>
+        <v>23875</v>
       </c>
       <c r="F6" t="n">
-        <v>160191</v>
+        <v>23896</v>
       </c>
       <c r="G6" t="n">
-        <v>256500</v>
+        <v>14811</v>
       </c>
       <c r="H6" t="n">
-        <v>64672</v>
+        <v>8140</v>
       </c>
       <c r="I6" t="n">
-        <v>7399</v>
+        <v>1316</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>52110</v>
+        <v>6591</v>
       </c>
       <c r="Z6" t="n">
-        <v>43017</v>
+        <v>5395</v>
       </c>
       <c r="AA6" t="n">
-        <v>87434</v>
+        <v>11026</v>
       </c>
       <c r="AB6" t="n">
-        <v>473159</v>
+        <v>59267</v>
       </c>
       <c r="AC6" t="n">
-        <v>55925</v>
+        <v>7014</v>
       </c>
       <c r="AD6" t="n">
-        <v>3848</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>153</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>10268</v>
+        <v>5529</v>
       </c>
       <c r="E7" t="n">
-        <v>180392</v>
+        <v>58960</v>
       </c>
       <c r="F7" t="n">
-        <v>583844</v>
+        <v>114960</v>
       </c>
       <c r="G7" t="n">
-        <v>281396</v>
+        <v>83086</v>
       </c>
       <c r="H7" t="n">
-        <v>2851100</v>
+        <v>219799</v>
       </c>
       <c r="I7" t="n">
-        <v>171089</v>
+        <v>28594</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>223</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>6486</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>237939</v>
+        <v>29968</v>
       </c>
       <c r="AB7" t="n">
-        <v>60821</v>
+        <v>7646</v>
       </c>
       <c r="AC7" t="n">
-        <v>3676427</v>
+        <v>460431</v>
       </c>
       <c r="AD7" t="n">
-        <v>96346</v>
+        <v>12050</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>207</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>288</v>
+        <v>121</v>
       </c>
       <c r="E8" t="n">
-        <v>13712</v>
+        <v>5622</v>
       </c>
       <c r="F8" t="n">
-        <v>33369</v>
+        <v>10267</v>
       </c>
       <c r="G8" t="n">
-        <v>23783</v>
+        <v>9866</v>
       </c>
       <c r="H8" t="n">
-        <v>332312</v>
+        <v>74487</v>
       </c>
       <c r="I8" t="n">
-        <v>1143451</v>
+        <v>93223</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>648</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>2648</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2126</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>100723</v>
+        <v>12636</v>
       </c>
       <c r="AD8" t="n">
-        <v>1440753</v>
+        <v>180245</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
